--- a/artfynd/A 55886-2023 artfynd.xlsx
+++ b/artfynd/A 55886-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114954322</v>
+        <v>114954328</v>
       </c>
       <c r="B2" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598510</v>
+        <v>598301</v>
       </c>
       <c r="R2" t="n">
-        <v>7208713</v>
+        <v>7208873</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114954323</v>
+        <v>114954318</v>
       </c>
       <c r="B3" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598336</v>
+        <v>598625</v>
       </c>
       <c r="R3" t="n">
-        <v>7208804</v>
+        <v>7208807</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114954328</v>
+        <v>114954319</v>
       </c>
       <c r="B4" t="n">
-        <v>90897</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598301</v>
+        <v>598512</v>
       </c>
       <c r="R4" t="n">
-        <v>7208873</v>
+        <v>7208710</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114954316</v>
+        <v>114954325</v>
       </c>
       <c r="B5" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598306</v>
+        <v>598336</v>
       </c>
       <c r="R5" t="n">
-        <v>7208849</v>
+        <v>7208804</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114954314</v>
+        <v>114954326</v>
       </c>
       <c r="B6" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598624</v>
+        <v>598313</v>
       </c>
       <c r="R6" t="n">
-        <v>7208809</v>
+        <v>7208841</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114954324</v>
+        <v>114954323</v>
       </c>
       <c r="B7" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598310</v>
+        <v>598336</v>
       </c>
       <c r="R7" t="n">
-        <v>7208844</v>
+        <v>7208804</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,12 +1320,7 @@
         <v>114954320</v>
       </c>
       <c r="B8" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114954326</v>
+        <v>114954321</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598313</v>
+        <v>598308</v>
       </c>
       <c r="R9" t="n">
-        <v>7208841</v>
+        <v>7208845</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1571,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114954321</v>
+        <v>114954314</v>
       </c>
       <c r="B10" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598308</v>
+        <v>598624</v>
       </c>
       <c r="R10" t="n">
-        <v>7208845</v>
+        <v>7208809</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114954317</v>
+        <v>114954315</v>
       </c>
       <c r="B11" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598301</v>
+        <v>598510</v>
       </c>
       <c r="R11" t="n">
-        <v>7208871</v>
+        <v>7208713</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114954325</v>
+        <v>114954316</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598336</v>
+        <v>598306</v>
       </c>
       <c r="R12" t="n">
-        <v>7208804</v>
+        <v>7208849</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114954318</v>
+        <v>114954317</v>
       </c>
       <c r="B13" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598625</v>
+        <v>598301</v>
       </c>
       <c r="R13" t="n">
-        <v>7208807</v>
+        <v>7208871</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,12 +1962,7 @@
         <v>114954329</v>
       </c>
       <c r="B14" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,55 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114954313</v>
+        <v>114954322</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarvsjöby, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598396</v>
+        <v>598510</v>
       </c>
       <c r="R15" t="n">
-        <v>7208732</v>
+        <v>7208713</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,15 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114954319</v>
+        <v>114954313</v>
       </c>
       <c r="B16" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,34 +2184,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skarvsjöby, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598512</v>
+        <v>598396</v>
       </c>
       <c r="R16" t="n">
-        <v>7208710</v>
+        <v>7208732</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,118 +2282,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>114954315</v>
-      </c>
-      <c r="B17" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Skarvsjöby, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>598510</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7208713</v>
-      </c>
-      <c r="S17" t="n">
-        <v>25</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
